--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8EA5BA-3743-49A5-B22C-AFF0D50C24A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7E4460-16BE-4FDF-81D5-D3BE4ED85532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="5025" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +52,18 @@
   </si>
   <si>
     <t>striker-球-自己 三点一线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类似AGVS向量式避碰导航</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/10/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向量避碰下的vice模式debug</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -377,10 +389,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.25" customWidth="1"/>
+    <col min="1" max="1" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -403,14 +415,30 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>

--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7E4460-16BE-4FDF-81D5-D3BE4ED85532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56419AC3-5F78-4760-AF4F-AE2C3BAD1D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="5025" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,14 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>AGVS导航</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>striker-球-自己 三点一线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>类似AGVS向量式避碰导航</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -64,6 +56,34 @@
   </si>
   <si>
     <t>向量避碰下的vice模式debug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走向点时，方向重叠带球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上避障或绕球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带预测的避障（动态避障）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加kick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有人踢小的，没人踢大的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/12/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>就个变量名大小写</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -389,13 +409,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.125" customWidth="1"/>
+    <col min="1" max="1" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -403,7 +424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -411,7 +432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -419,27 +440,44 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56419AC3-5F78-4760-AF4F-AE2C3BAD1D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D461C2B-BE09-480C-A4F0-75275D9884C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14175" yWindow="1725" windowWidth="24090" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>上避障或绕球</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>带预测的避障（动态避障）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,6 +80,14 @@
   </si>
   <si>
     <t>就个变量名大小写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/16/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上避障</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -452,8 +456,11 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -461,23 +468,23 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D461C2B-BE09-480C-A4F0-75275D9884C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803E467D-778A-4C7C-AB0C-BD07C0410058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14175" yWindow="1725" windowWidth="24090" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9315" yWindow="3450" windowWidth="24510" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,6 +88,86 @@
   </si>
   <si>
     <t>上避障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>走向点时，方向重叠带球
+（踢掉agvs，干扰拦截）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/20/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>判死刑，干不了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/1/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x象限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>y象限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等 to 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等 to 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>友位置 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我位置 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌位置 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>球位置 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谁近谁踢</t>
+  </si>
+  <si>
+    <t>谁近谁踢</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -95,7 +175,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +190,105 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <gradientFill>
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="0.5">
+          <color rgb="FFFFFF00"/>
+        </stop>
+        <stop position="1">
+          <color theme="0"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill>
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="0.5">
+          <color rgb="FFFF0000"/>
+        </stop>
+        <stop position="1">
+          <color theme="0"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="1">
+          <color theme="4" tint="0.40000610370189521"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="0.5">
+          <color theme="4"/>
+        </stop>
+        <stop position="1">
+          <color theme="0"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color theme="0"/>
+        </stop>
+        <stop position="0.5">
+          <color theme="9" tint="0.40000610370189521"/>
+        </stop>
+        <stop position="1">
+          <color theme="0"/>
+        </stop>
+      </gradientFill>
     </fill>
   </fills>
   <borders count="1">
@@ -131,8 +303,54 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -413,81 +631,486 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.125" customWidth="1"/>
-    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="10" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="7">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1</v>
+      </c>
+      <c r="H2" s="11">
+        <v>2</v>
+      </c>
+      <c r="I2" s="11">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" s="11"/>
+      <c r="E3" s="6">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5">
+        <v>4</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="4">
+        <v>4</v>
+      </c>
+      <c r="K3" s="16"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="4">
+        <v>4</v>
+      </c>
+      <c r="K5" s="16"/>
+      <c r="L5" s="11"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="G6" s="11"/>
+      <c r="H6" s="11">
+        <v>3</v>
+      </c>
+      <c r="I6" s="11">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="4">
+        <v>4</v>
+      </c>
+      <c r="K7" s="15"/>
+      <c r="L7" s="11"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11">
+        <v>4</v>
+      </c>
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="13"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="4">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="2"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="2"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="4">
+        <v>4</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
+      <c r="G12" s="11">
+        <v>4</v>
+      </c>
+      <c r="H12" s="11">
+        <v>2</v>
+      </c>
+      <c r="I12" s="11">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="2"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="4">
+        <v>4</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="2"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="2"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="4">
+        <v>4</v>
+      </c>
+      <c r="K15" s="17"/>
+      <c r="L15" s="11"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="2"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11">
+        <v>3</v>
+      </c>
+      <c r="I16" s="11">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="2"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="4">
+        <v>4</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="11"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="2"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11">
+        <v>4</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="2"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="4">
+        <v>4</v>
+      </c>
+      <c r="K19" s="18"/>
+      <c r="L19" s="11"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B20" s="2"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="4">
+        <v>1</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="2"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="4">
+        <v>4</v>
+      </c>
+      <c r="I21" s="4">
+        <v>4</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="2"/>
+      <c r="G22" s="4">
+        <v>2</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J22" s="4"/>
+      <c r="K22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="2"/>
+      <c r="G23" s="4">
+        <v>3</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="4"/>
+      <c r="K23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
     </row>
   </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="G12:G21"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="G2:G11"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H12:H15"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803E467D-778A-4C7C-AB0C-BD07C0410058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1D3463-AB79-486D-95EB-BCD3CE829449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9315" yWindow="3450" windowWidth="24510" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5610" yWindow="3480" windowWidth="24510" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,6 +168,30 @@
   </si>
   <si>
     <t>谁近谁踢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改进的策略，需要新的2种状态机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>k2oppo状态机完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/4/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>k2mate状态机完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试debug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只是初稿，估计一堆逻辑bug</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -303,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -330,26 +354,25 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.125" customWidth="1"/>
@@ -648,10 +671,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="12"/>
+      <c r="F1" s="17"/>
       <c r="G1" s="3" t="s">
         <v>33</v>
       </c>
@@ -672,7 +695,7 @@
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="7">
@@ -681,22 +704,22 @@
       <c r="F2" s="8">
         <v>1</v>
       </c>
-      <c r="G2" s="11">
-        <v>1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="12">
+        <v>1</v>
+      </c>
+      <c r="H2" s="12">
         <v>2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>1</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -707,21 +730,21 @@
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="6">
         <v>3</v>
       </c>
       <c r="F3" s="5">
         <v>4</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
       <c r="J3" s="4">
         <v>4</v>
       </c>
-      <c r="K3" s="16"/>
-      <c r="L3" s="11"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -730,18 +753,18 @@
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11">
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12">
         <v>4</v>
       </c>
       <c r="J4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="11"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -753,14 +776,14 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="4">
         <v>4</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="11"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -772,20 +795,20 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11">
+      <c r="G6" s="12"/>
+      <c r="H6" s="12">
         <v>3</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="12">
         <v>1</v>
       </c>
       <c r="J6" s="4">
         <v>1</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -796,14 +819,14 @@
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
       <c r="J7" s="4">
         <v>4</v>
       </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="11"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -815,9 +838,9 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11">
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12">
         <v>4</v>
       </c>
       <c r="J8" s="4">
@@ -826,7 +849,7 @@
       <c r="K8" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="13"/>
+      <c r="L8" s="11"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -836,22 +859,25 @@
       <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
       <c r="J9" s="4">
         <v>4</v>
       </c>
       <c r="K9" t="s">
         <v>27</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
       <c r="B10" s="2"/>
-      <c r="G10" s="11"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="4">
         <v>1</v>
       </c>
@@ -866,8 +892,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
-      <c r="G11" s="11"/>
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="12"/>
       <c r="H11" s="4">
         <v>4</v>
       </c>
@@ -880,19 +914,22 @@
       <c r="K11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
       <c r="B12" s="2"/>
-      <c r="G12" s="11">
-        <v>4</v>
-      </c>
-      <c r="H12" s="11">
+      <c r="G12" s="12">
+        <v>4</v>
+      </c>
+      <c r="H12" s="12">
         <v>2</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="12">
         <v>1</v>
       </c>
       <c r="J12" s="4">
@@ -901,15 +938,18 @@
       <c r="K12" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
       <c r="B13" s="2"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="4">
         <v>4</v>
       </c>
@@ -919,91 +959,91 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11">
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12">
         <v>4</v>
       </c>
       <c r="J14" s="4">
         <v>1</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="4">
         <v>4</v>
       </c>
-      <c r="K15" s="17"/>
-      <c r="L15" s="11"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="12"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11">
+      <c r="G16" s="12"/>
+      <c r="H16" s="12">
         <v>3</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="12">
         <v>1</v>
       </c>
       <c r="J16" s="4">
         <v>1</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="4">
         <v>4</v>
       </c>
-      <c r="K17" s="18"/>
-      <c r="L17" s="11"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="12"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="2"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11">
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12">
         <v>4</v>
       </c>
       <c r="J18" s="4">
         <v>1</v>
       </c>
-      <c r="K18" s="18" t="s">
+      <c r="K18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="11"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="2"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="4">
         <v>4</v>
       </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="11"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="2"/>
-      <c r="G20" s="11"/>
+      <c r="G20" s="12"/>
       <c r="H20" s="4">
         <v>1</v>
       </c>
@@ -1016,13 +1056,13 @@
       <c r="K20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="2"/>
-      <c r="G21" s="11"/>
+      <c r="G21" s="12"/>
       <c r="H21" s="4">
         <v>4</v>
       </c>
@@ -1068,32 +1108,13 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-    </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="G2:G11"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H12:H15"/>
     <mergeCell ref="G12:G21"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
@@ -1105,11 +1126,16 @@
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="G2:G11"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L16:L19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1D3463-AB79-486D-95EB-BCD3CE829449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B225ED2E-7F2E-4DA6-A301-A8C892E6CC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5610" yWindow="3480" windowWidth="24510" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -187,11 +187,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>测试debug</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>只是初稿，估计一堆逻辑bug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/3/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -357,6 +361,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -364,15 +377,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -671,10 +675,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="17"/>
+      <c r="F1" s="12"/>
       <c r="G1" s="3" t="s">
         <v>33</v>
       </c>
@@ -695,7 +699,7 @@
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="7">
@@ -704,22 +708,22 @@
       <c r="F2" s="8">
         <v>1</v>
       </c>
-      <c r="G2" s="12">
-        <v>1</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="G2" s="13">
+        <v>1</v>
+      </c>
+      <c r="H2" s="13">
         <v>2</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>1</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -730,21 +734,21 @@
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="D3" s="13"/>
       <c r="E3" s="6">
         <v>3</v>
       </c>
       <c r="F3" s="5">
         <v>4</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
       <c r="J3" s="4">
         <v>4</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="12"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="13"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -753,18 +757,18 @@
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12">
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13">
         <v>4</v>
       </c>
       <c r="J4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="12"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -776,14 +780,14 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
       <c r="J5" s="4">
         <v>4</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="12"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="13"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -795,20 +799,20 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12">
+      <c r="G6" s="13"/>
+      <c r="H6" s="13">
         <v>3</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="13">
         <v>1</v>
       </c>
       <c r="J6" s="4">
         <v>1</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -819,14 +823,14 @@
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
       <c r="J7" s="4">
         <v>4</v>
       </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="12"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -838,9 +842,9 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13">
         <v>4</v>
       </c>
       <c r="J8" s="4">
@@ -859,9 +863,9 @@
       <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
       <c r="J9" s="4">
         <v>4</v>
       </c>
@@ -877,7 +881,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="13"/>
       <c r="H10" s="4">
         <v>1</v>
       </c>
@@ -899,9 +903,9 @@
         <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="G11" s="13"/>
       <c r="H11" s="4">
         <v>4</v>
       </c>
@@ -920,16 +924,21 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="G12" s="12">
-        <v>4</v>
-      </c>
-      <c r="H12" s="12">
+        <v>39</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="13">
+        <v>4</v>
+      </c>
+      <c r="H12" s="13">
         <v>2</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <v>1</v>
       </c>
       <c r="J12" s="4">
@@ -943,13 +952,9 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
       <c r="J13" s="4">
         <v>4</v>
       </c>
@@ -959,91 +964,91 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12">
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13">
         <v>4</v>
       </c>
       <c r="J14" s="4">
         <v>1</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="L14" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
       <c r="J15" s="4">
         <v>4</v>
       </c>
-      <c r="K15" s="13"/>
-      <c r="L15" s="12"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12">
+      <c r="G16" s="13"/>
+      <c r="H16" s="13">
         <v>3</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <v>1</v>
       </c>
       <c r="J16" s="4">
         <v>1</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
       <c r="J17" s="4">
         <v>4</v>
       </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="12"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="13"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="2"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12">
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13">
         <v>4</v>
       </c>
       <c r="J18" s="4">
         <v>1</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="12"/>
+      <c r="L18" s="13"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="2"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
       <c r="J19" s="4">
         <v>4</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="12"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="13"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="2"/>
-      <c r="G20" s="12"/>
+      <c r="G20" s="13"/>
       <c r="H20" s="4">
         <v>1</v>
       </c>
@@ -1062,7 +1067,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="2"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="13"/>
       <c r="H21" s="4">
         <v>4</v>
       </c>
@@ -1110,12 +1115,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="G2:G11"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="G12:G21"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L16:L19"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="L2:L5"/>
@@ -1126,16 +1135,12 @@
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="H16:H19"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L16:L19"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="G2:G11"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="G12:G21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B225ED2E-7F2E-4DA6-A301-A8C892E6CC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90238609-2BAF-4CC7-A5F8-EEA785516BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="765" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -196,6 +196,18 @@
   </si>
   <si>
     <t>同上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整体可运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/3/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上位状态机没测试，k2m不完全</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -361,9 +373,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -372,11 +387,8 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,7 +674,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.125" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="32.5" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="10" width="13.875" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
@@ -675,10 +687,10 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="12"/>
+      <c r="F1" s="17"/>
       <c r="G1" s="3" t="s">
         <v>33</v>
       </c>
@@ -699,7 +711,7 @@
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="7">
@@ -708,22 +720,22 @@
       <c r="F2" s="8">
         <v>1</v>
       </c>
-      <c r="G2" s="13">
-        <v>1</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="G2" s="12">
+        <v>1</v>
+      </c>
+      <c r="H2" s="12">
         <v>2</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <v>1</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -734,21 +746,21 @@
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="6">
         <v>3</v>
       </c>
       <c r="F3" s="5">
         <v>4</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
       <c r="J3" s="4">
         <v>4</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="13"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -757,18 +769,18 @@
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13">
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12">
         <v>4</v>
       </c>
       <c r="J4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="13"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -780,14 +792,14 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="4">
         <v>4</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="13"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -799,20 +811,20 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13">
+      <c r="G6" s="12"/>
+      <c r="H6" s="12">
         <v>3</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <v>1</v>
       </c>
       <c r="J6" s="4">
         <v>1</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="12" t="s">
         <v>35</v>
       </c>
     </row>
@@ -823,14 +835,14 @@
       <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
       <c r="J7" s="4">
         <v>4</v>
       </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="13"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -842,9 +854,9 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13">
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12">
         <v>4</v>
       </c>
       <c r="J8" s="4">
@@ -863,9 +875,9 @@
       <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
       <c r="J9" s="4">
         <v>4</v>
       </c>
@@ -881,7 +893,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="G10" s="13"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="4">
         <v>1</v>
       </c>
@@ -905,7 +917,7 @@
       <c r="C11" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="4">
         <v>4</v>
       </c>
@@ -932,13 +944,13 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="13">
-        <v>4</v>
-      </c>
-      <c r="H12" s="13">
+      <c r="G12" s="12">
+        <v>4</v>
+      </c>
+      <c r="H12" s="12">
         <v>2</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <v>1</v>
       </c>
       <c r="J12" s="4">
@@ -952,9 +964,18 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="4">
         <v>4</v>
       </c>
@@ -964,91 +985,91 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13">
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12">
         <v>4</v>
       </c>
       <c r="J14" s="4">
         <v>1</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="4">
         <v>4</v>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="12"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B16" s="2"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13">
+      <c r="G16" s="12"/>
+      <c r="H16" s="12">
         <v>3</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <v>1</v>
       </c>
       <c r="J16" s="4">
         <v>1</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="2"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="4">
         <v>4</v>
       </c>
-      <c r="K17" s="17"/>
-      <c r="L17" s="13"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="12"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="2"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13">
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12">
         <v>4</v>
       </c>
       <c r="J18" s="4">
         <v>1</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="13"/>
+      <c r="L18" s="12"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="2"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="4">
         <v>4</v>
       </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="13"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="2"/>
-      <c r="G20" s="13"/>
+      <c r="G20" s="12"/>
       <c r="H20" s="4">
         <v>1</v>
       </c>
@@ -1067,7 +1088,7 @@
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="2"/>
-      <c r="G21" s="13"/>
+      <c r="G21" s="12"/>
       <c r="H21" s="4">
         <v>4</v>
       </c>
@@ -1115,6 +1136,22 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="G2:G11"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="G12:G21"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="I14:I15"/>
     <mergeCell ref="K14:K15"/>
@@ -1125,22 +1162,6 @@
     <mergeCell ref="K16:K17"/>
     <mergeCell ref="K18:K19"/>
     <mergeCell ref="L16:L19"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="L2:L5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="G2:G11"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="G12:G21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/controllers/Nao_defender/改进表.xlsx
+++ b/controllers/Nao_defender/改进表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Mrobotic\TDP\Nao_test_keeperAndDefender\controllers\Nao_defender\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90238609-2BAF-4CC7-A5F8-EEA785516BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1064B60-AE54-4AD1-8EF2-33265CDAC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="765" yWindow="4545" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11295" yWindow="2430" windowWidth="26055" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="49">
   <si>
     <t>改进/修复</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -208,6 +208,18 @@
   </si>
   <si>
     <t>上位状态机没测试，k2m不完全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16/3/2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pKick尝试但失败，绕球改了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pw kick 融合，修改绕球，debug</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -984,7 +996,15 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="2"/>
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12">
